--- a/Tweaks/Web Browsers Configuration/Firefox/about.config firefox.xlsx
+++ b/Tweaks/Web Browsers Configuration/Firefox/about.config firefox.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/50cb2a26af6a7a83/CyberSecHome/Web Browsers Configuration/Firefox/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/50cb2a26af6a7a83/CyberSecHome/Tweaks/Web Browsers Configuration/Firefox/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{9EE6A70E-23D5-410F-902C-F038E2EDDAEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E8172AE-6B68-465F-AA1F-57AD5DEE15DB}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{9EE6A70E-23D5-410F-902C-F038E2EDDAEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE4FB157-2DD6-4828-983F-17471892FF01}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="0" windowWidth="10400" windowHeight="12160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1693" yWindow="1787" windowWidth="15360" windowHeight="8780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="185">
   <si>
     <t>privacy.resistFingerprinting</t>
   </si>
@@ -577,6 +577,9 @@
   </si>
   <si>
     <t>dom.ipc.processPriorityManager.backgroundUsesEcoQoS</t>
+  </si>
+  <si>
+    <t>false for better anti fingerprint. True for better performance</t>
   </si>
 </sst>
 </file>
@@ -734,6 +737,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -999,7 +1006,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G164"/>
   <sheetFormatPr defaultRowHeight="14.35"/>
   <cols>
     <col min="1" max="1" width="58.41015625" customWidth="1"/>
@@ -1014,7 +1021,7 @@
     <col min="10" max="10" width="35.3515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>124</v>
       </c>
@@ -1024,17 +1031,8 @@
       <c r="C1" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1044,17 +1042,8 @@
       <c r="C2" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1064,17 +1053,8 @@
       <c r="C3" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1084,17 +1064,8 @@
       <c r="C4" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -1104,17 +1075,8 @@
       <c r="C5" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
@@ -1124,17 +1086,8 @@
       <c r="C6" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="D6" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
@@ -1144,17 +1097,8 @@
       <c r="C7" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="D7" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
@@ -1162,14 +1106,8 @@
         <v>0</v>
       </c>
       <c r="C8" s="1"/>
-      <c r="E8" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
@@ -1177,14 +1115,8 @@
         <v>0</v>
       </c>
       <c r="C9" s="1"/>
-      <c r="E9" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>177</v>
       </c>
@@ -1192,14 +1124,8 @@
         <v>4000000</v>
       </c>
       <c r="C10" s="1"/>
-      <c r="E10" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
         <v>8</v>
       </c>
@@ -1207,14 +1133,8 @@
         <v>0</v>
       </c>
       <c r="C11" s="1"/>
-      <c r="E11" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" s="3" t="s">
         <v>9</v>
       </c>
@@ -1222,14 +1142,8 @@
         <v>0</v>
       </c>
       <c r="C12" s="1"/>
-      <c r="E12" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" s="3" t="s">
         <v>10</v>
       </c>
@@ -1237,14 +1151,8 @@
         <v>0</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="E13" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14" s="3" t="s">
         <v>11</v>
       </c>
@@ -1252,14 +1160,8 @@
         <v>1</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="E14" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" s="3" t="s">
         <v>12</v>
       </c>
@@ -1267,14 +1169,8 @@
         <v>1</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="E15" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" s="3" t="s">
         <v>13</v>
       </c>
@@ -1282,14 +1178,8 @@
         <v>1</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="E16" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" s="3" t="s">
         <v>14</v>
       </c>
@@ -1297,29 +1187,19 @@
         <v>1</v>
       </c>
       <c r="C17" s="1"/>
-      <c r="E17" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B18" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="C18" s="1"/>
-      <c r="E18" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>0</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" s="3" t="s">
         <v>16</v>
       </c>
@@ -1327,14 +1207,8 @@
         <v>0</v>
       </c>
       <c r="C19" s="1"/>
-      <c r="E19" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" s="3" t="s">
         <v>17</v>
       </c>
@@ -1342,14 +1216,8 @@
         <v>1</v>
       </c>
       <c r="C20" s="1"/>
-      <c r="E20" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21" s="3" t="s">
         <v>18</v>
       </c>
@@ -1357,14 +1225,8 @@
         <v>0</v>
       </c>
       <c r="C21" s="1"/>
-      <c r="E21" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22" s="3" t="s">
         <v>19</v>
       </c>
@@ -1372,12 +1234,8 @@
         <v>1</v>
       </c>
       <c r="C22" s="1"/>
-      <c r="E22" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="F22" s="4"/>
-    </row>
-    <row r="23" spans="1:6">
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
         <v>20</v>
       </c>
@@ -1385,12 +1243,8 @@
         <v>147</v>
       </c>
       <c r="C23" s="1"/>
-      <c r="E23" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="F23" s="4"/>
-    </row>
-    <row r="24" spans="1:6">
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
         <v>21</v>
       </c>
@@ -1398,12 +1252,8 @@
         <v>0</v>
       </c>
       <c r="C24" s="1"/>
-      <c r="E24" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="F24" s="4"/>
-    </row>
-    <row r="25" spans="1:6">
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
         <v>22</v>
       </c>
@@ -1411,12 +1261,8 @@
         <v>0</v>
       </c>
       <c r="C25" s="1"/>
-      <c r="E25" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="F25" s="4"/>
-    </row>
-    <row r="26" spans="1:6">
+    </row>
+    <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
         <v>23</v>
       </c>
@@ -1424,14 +1270,8 @@
         <v>0</v>
       </c>
       <c r="C26" s="1"/>
-      <c r="E26" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27" s="3" t="s">
         <v>24</v>
       </c>
@@ -1439,14 +1279,8 @@
         <v>0</v>
       </c>
       <c r="C27" s="1"/>
-      <c r="E27" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+    </row>
+    <row r="28" spans="1:3">
       <c r="A28" s="3" t="s">
         <v>25</v>
       </c>
@@ -1454,14 +1288,8 @@
         <v>0</v>
       </c>
       <c r="C28" s="1"/>
-      <c r="E28" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+    </row>
+    <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
         <v>26</v>
       </c>
@@ -1469,14 +1297,8 @@
         <v>0</v>
       </c>
       <c r="C29" s="1"/>
-      <c r="E29" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30" s="3" t="s">
         <v>27</v>
       </c>
@@ -1484,14 +1306,8 @@
         <v>0</v>
       </c>
       <c r="C30" s="1"/>
-      <c r="E30" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+    </row>
+    <row r="31" spans="1:3">
       <c r="A31" s="3" t="s">
         <v>28</v>
       </c>
@@ -1499,14 +1315,8 @@
         <v>0</v>
       </c>
       <c r="C31" s="1"/>
-      <c r="E31" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+    </row>
+    <row r="32" spans="1:3">
       <c r="A32" s="3" t="s">
         <v>29</v>
       </c>
@@ -1514,12 +1324,6 @@
         <v>0</v>
       </c>
       <c r="C32" s="1"/>
-      <c r="E32" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>107</v>
-      </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="3" t="s">
@@ -1529,12 +1333,6 @@
         <v>0</v>
       </c>
       <c r="C33" s="1"/>
-      <c r="E33" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>118</v>
-      </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="3" t="s">
@@ -1544,12 +1342,6 @@
         <v>0</v>
       </c>
       <c r="C34" s="1"/>
-      <c r="E34" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>118</v>
-      </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="3" t="s">
@@ -1559,12 +1351,6 @@
         <v>0</v>
       </c>
       <c r="C35" s="1"/>
-      <c r="E35" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>118</v>
-      </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="3" t="s">
@@ -1574,12 +1360,6 @@
         <v>1</v>
       </c>
       <c r="C36" s="1"/>
-      <c r="E36" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>118</v>
-      </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="3" t="s">
@@ -1589,12 +1369,6 @@
         <v>1</v>
       </c>
       <c r="C37" s="1"/>
-      <c r="E37" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>118</v>
-      </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="3" t="s">
@@ -1604,12 +1378,6 @@
         <v>1</v>
       </c>
       <c r="C38" s="1"/>
-      <c r="E38" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>76</v>
-      </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="3" t="s">
@@ -1619,12 +1387,6 @@
         <v>1</v>
       </c>
       <c r="C39" s="1"/>
-      <c r="E39" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>76</v>
-      </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="3" t="s">
@@ -1634,12 +1396,6 @@
         <v>1</v>
       </c>
       <c r="C40" s="1"/>
-      <c r="E40" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>122</v>
-      </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="3" t="s">
@@ -1649,12 +1405,6 @@
         <v>1</v>
       </c>
       <c r="C41" s="1"/>
-      <c r="E41" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>174</v>
-      </c>
       <c r="G41" s="4"/>
     </row>
     <row r="42" spans="1:7">
@@ -1665,12 +1415,6 @@
         <v>1</v>
       </c>
       <c r="C42" s="1"/>
-      <c r="E42" t="s">
-        <v>175</v>
-      </c>
-      <c r="F42" s="16" t="s">
-        <v>176</v>
-      </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="3" t="s">
@@ -2233,6 +1977,369 @@
       </c>
       <c r="B108" s="14" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" s="6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="10" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="11" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B144" s="4"/>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B145" s="4"/>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B146" s="4"/>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B147" s="4"/>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" t="s">
+        <v>175</v>
+      </c>
+      <c r="B164" s="16" t="s">
+        <v>176</v>
       </c>
     </row>
   </sheetData>

--- a/Tweaks/Web Browsers Configuration/Firefox/about.config firefox.xlsx
+++ b/Tweaks/Web Browsers Configuration/Firefox/about.config firefox.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/50cb2a26af6a7a83/CyberSecHome/Tweaks/Web Browsers Configuration/Firefox/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{9EE6A70E-23D5-410F-902C-F038E2EDDAEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE4FB157-2DD6-4828-983F-17471892FF01}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{9EE6A70E-23D5-410F-902C-F038E2EDDAEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9ECED37E-BE38-42CB-A9BD-5F62B7EEA00C}"/>
   <bookViews>
-    <workbookView xWindow="1693" yWindow="1787" windowWidth="15360" windowHeight="8780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="186">
   <si>
     <t>privacy.resistFingerprinting</t>
   </si>
@@ -72,9 +72,6 @@
     <t>gfx.color_management.mode</t>
   </si>
   <si>
-    <t>dom.webgpu.enabled</t>
-  </si>
-  <si>
     <t>network.http.http3.enable</t>
   </si>
   <si>
@@ -447,12 +444,6 @@
     <t>device.sensors.enabled</t>
   </si>
   <si>
-    <t>privacy.firstparty.isolate</t>
-  </si>
-  <si>
-    <t>some issues with cross</t>
-  </si>
-  <si>
     <t>privacy.firstparty.isolate.block_post_message</t>
   </si>
   <si>
@@ -579,7 +570,19 @@
     <t>dom.ipc.processPriorityManager.backgroundUsesEcoQoS</t>
   </si>
   <si>
-    <t>false for better anti fingerprint. True for better performance</t>
+    <t xml:space="preserve">browser.privatebrowsing.forceMediaMemoryCache </t>
+  </si>
+  <si>
+    <t>privacy.spoof_english</t>
+  </si>
+  <si>
+    <t>privacy.trackingprotection.content.protection.enabled</t>
+  </si>
+  <si>
+    <t>privacy.resistFingerprinting.letterboxing</t>
+  </si>
+  <si>
+    <t>For better anti finger print need to change screen scalability to lower. Will set a frame around the screen.</t>
   </si>
 </sst>
 </file>
@@ -1006,30 +1009,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G164"/>
-  <sheetFormatPr defaultRowHeight="14.35"/>
+  <dimension ref="A1:G165"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="58.41015625" customWidth="1"/>
-    <col min="2" max="2" width="67.87890625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="61.76171875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="43.41015625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="43.3515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.76171875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.3515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.87890625" customWidth="1"/>
-    <col min="9" max="9" width="22.76171875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="35.3515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="58.3984375" customWidth="1"/>
+    <col min="2" max="2" width="67.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="88.9296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="43.3984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.73046875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.86328125" customWidth="1"/>
+    <col min="9" max="9" width="22.73046875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="35.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1040,7 +1042,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1051,7 +1053,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1062,7 +1064,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1073,7 +1075,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1084,7 +1086,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1095,7 +1097,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1118,7 +1120,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B10" s="8">
         <v>4000000</v>
@@ -1189,19 +1191,13 @@
       <c r="C17" s="1"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>184</v>
-      </c>
+      <c r="A18" s="3"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="1"/>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B19" s="8" t="b">
         <v>0</v>
@@ -1210,7 +1206,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B20" s="8" t="b">
         <v>1</v>
@@ -1219,7 +1215,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" s="8" t="b">
         <v>0</v>
@@ -1228,7 +1224,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B22" s="8" t="b">
         <v>1</v>
@@ -1237,16 +1233,16 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C23" s="1"/>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B24" s="8" t="b">
         <v>0</v>
@@ -1255,7 +1251,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B25" s="8" t="b">
         <v>0</v>
@@ -1264,7 +1260,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B26" s="8" t="b">
         <v>0</v>
@@ -1273,7 +1269,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B27" s="8" t="b">
         <v>0</v>
@@ -1282,7 +1278,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B28" s="8" t="b">
         <v>0</v>
@@ -1291,7 +1287,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B29" s="8" t="b">
         <v>0</v>
@@ -1300,7 +1296,7 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B30" s="8" t="b">
         <v>0</v>
@@ -1309,7 +1305,7 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B31" s="8" t="b">
         <v>0</v>
@@ -1318,7 +1314,7 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B32" s="8" t="b">
         <v>0</v>
@@ -1327,7 +1323,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B33" s="8" t="b">
         <v>0</v>
@@ -1336,7 +1332,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B34" s="8" t="b">
         <v>0</v>
@@ -1345,7 +1341,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B35" s="8" t="b">
         <v>0</v>
@@ -1354,7 +1350,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B36" s="8" t="b">
         <v>1</v>
@@ -1363,7 +1359,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B37" s="8" t="b">
         <v>1</v>
@@ -1372,7 +1368,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B38" s="8" t="b">
         <v>1</v>
@@ -1381,7 +1377,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B39" s="8" t="b">
         <v>1</v>
@@ -1390,7 +1386,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B40" s="8" t="b">
         <v>1</v>
@@ -1399,7 +1395,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B41" s="8" t="b">
         <v>1</v>
@@ -1409,7 +1405,7 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B42" s="8" t="b">
         <v>1</v>
@@ -1418,7 +1414,7 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B43" s="8" t="b">
         <v>1</v>
@@ -1427,7 +1423,7 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" s="8" t="b">
         <v>1</v>
@@ -1436,7 +1432,7 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B45" s="8" t="b">
         <v>1</v>
@@ -1445,7 +1441,7 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B46" s="8" t="b">
         <v>1</v>
@@ -1454,7 +1450,7 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B47" s="8" t="b">
         <v>1</v>
@@ -1463,7 +1459,7 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B48" s="8" t="b">
         <v>1</v>
@@ -1472,7 +1468,7 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B49" s="8" t="b">
         <v>1</v>
@@ -1481,7 +1477,7 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" s="8" t="b">
         <v>0</v>
@@ -1490,18 +1486,18 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B51" s="8" t="b">
         <v>0</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B52" s="8" t="b">
         <v>0</v>
@@ -1510,7 +1506,7 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B53" s="8" t="b">
         <v>0</v>
@@ -1519,7 +1515,7 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B54" s="8" t="b">
         <v>0</v>
@@ -1528,7 +1524,7 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B55" s="8" t="b">
         <v>1</v>
@@ -1537,16 +1533,16 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="C56" s="1"/>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B57" s="8" t="b">
         <v>0</v>
@@ -1555,7 +1551,7 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B58" s="8" t="b">
         <v>1</v>
@@ -1564,7 +1560,7 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B59" s="8" t="b">
         <v>0</v>
@@ -1573,7 +1569,7 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B60" s="8" t="b">
         <v>0</v>
@@ -1582,7 +1578,7 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B61" s="3">
         <v>2</v>
@@ -1591,7 +1587,7 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B62" s="3" t="b">
         <v>0</v>
@@ -1600,18 +1596,18 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B63" s="3">
         <v>1</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B64" s="3" t="b">
         <v>0</v>
@@ -1620,7 +1616,7 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B65" s="3" t="b">
         <v>0</v>
@@ -1629,18 +1625,18 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B66" s="3">
         <v>32</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B67" s="8" t="b">
         <v>1</v>
@@ -1649,7 +1645,7 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B68" s="3" t="b">
         <v>0</v>
@@ -1657,18 +1653,18 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B69" s="9">
         <v>20</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B70" s="3" t="b">
         <v>0</v>
@@ -1676,18 +1672,18 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B71" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C71" s="4" t="s">
         <v>132</v>
-      </c>
-      <c r="B71" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B72" s="8" t="b">
         <v>1</v>
@@ -1695,7 +1691,7 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="4" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B73" s="3" t="b">
         <v>0</v>
@@ -1703,7 +1699,7 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B74" s="3" t="b">
         <v>0</v>
@@ -1711,7 +1707,7 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B75" s="3" t="b">
         <v>0</v>
@@ -1719,7 +1715,7 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B76" s="3" t="b">
         <v>0</v>
@@ -1727,7 +1723,7 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B77" s="3" t="b">
         <v>0</v>
@@ -1735,7 +1731,7 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B78" s="3" t="b">
         <v>0</v>
@@ -1743,18 +1739,15 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B79" s="8" t="b">
         <v>1</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B80" s="8" t="b">
         <v>1</v>
@@ -1762,47 +1755,55 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B81" s="8" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B82" s="8" t="b">
-        <v>1</v>
+      <c r="A82" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="B82" s="14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="B83" s="13" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="B84" s="14" t="b">
-        <v>0</v>
+      <c r="B84" s="13" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="B85" s="13" t="s">
-        <v>152</v>
+      <c r="B85" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="B86" s="13" t="s">
         <v>152</v>
+      </c>
+      <c r="B86" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B87" s="14" t="b">
         <v>0</v>
@@ -1810,7 +1811,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B88" s="14" t="b">
         <v>0</v>
@@ -1818,7 +1819,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B89" s="14" t="b">
         <v>0</v>
@@ -1826,15 +1827,15 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="B90" s="14" t="b">
-        <v>0</v>
+        <v>156</v>
+      </c>
+      <c r="B90" s="14" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B91" s="14" t="b">
         <v>0</v>
@@ -1842,15 +1843,15 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="B92" s="14" t="s">
-        <v>152</v>
+        <v>158</v>
+      </c>
+      <c r="B92" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B93" s="14" t="b">
         <v>0</v>
@@ -1858,15 +1859,15 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="B94" s="14" t="b">
-        <v>0</v>
+        <v>160</v>
+      </c>
+      <c r="B94" s="15" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B95" s="14" t="b">
         <v>0</v>
@@ -1874,472 +1875,491 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="B96" s="15" t="s">
-        <v>152</v>
+        <v>162</v>
+      </c>
+      <c r="B96" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="B97" s="14" t="b">
-        <v>0</v>
+        <v>163</v>
+      </c>
+      <c r="B97" s="14" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="B98" s="14" t="b">
-        <v>0</v>
+        <v>164</v>
+      </c>
+      <c r="B98" s="14" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="B99" s="14" t="s">
-        <v>152</v>
+        <v>165</v>
+      </c>
+      <c r="B99" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="B100" s="14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" t="s">
         <v>167</v>
       </c>
-      <c r="B100" s="14" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3">
-      <c r="A101" s="13" t="s">
+      <c r="B101" s="14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" t="s">
         <v>168</v>
       </c>
-      <c r="B101" s="14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3">
-      <c r="A102" s="13" t="s">
-        <v>169</v>
-      </c>
       <c r="B102" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:3">
-      <c r="A103" t="s">
-        <v>170</v>
-      </c>
-      <c r="B103" s="14" t="b">
-        <v>0</v>
+      <c r="A103" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="B103" s="14">
+        <v>32</v>
+      </c>
+      <c r="C103" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="B104" s="14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:3">
-      <c r="A105" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="B105" s="14">
-        <v>32</v>
-      </c>
-      <c r="C105" t="s">
+      <c r="A105" t="s">
         <v>179</v>
+      </c>
+      <c r="B105" s="14" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
+        <v>180</v>
+      </c>
+      <c r="B106" s="14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="B106" s="14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3">
-      <c r="A107" t="s">
+      <c r="B107" s="14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="B107" s="14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3">
-      <c r="A108" t="s">
+      <c r="B108" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" t="s">
         <v>183</v>
       </c>
-      <c r="B108" s="14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3">
-      <c r="A111" s="5" t="s">
+      <c r="B109" s="14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" t="s">
+        <v>184</v>
+      </c>
+      <c r="B110" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="C110" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="6" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="6" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="112" spans="1:3">
-      <c r="A112" s="6" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2">
-      <c r="A113" s="6" t="s">
+    <row r="118" spans="1:2">
+      <c r="A118" s="6" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="114" spans="1:2">
-      <c r="A114" s="6" t="s">
+    <row r="119" spans="1:2">
+      <c r="A119" s="6" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="115" spans="1:2">
-      <c r="A115" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2">
-      <c r="A116" s="10" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2">
-      <c r="A117" s="11" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2">
-      <c r="A123" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>125</v>
+    <row r="120" spans="1:2">
+      <c r="A120" s="10" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="11" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="124" spans="1:2">
-      <c r="A124" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B124" s="4" t="s">
-        <v>72</v>
+      <c r="A124" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B144" s="4"/>
+        <v>98</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B145" s="4"/>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B146" s="4"/>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B147" s="4"/>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B148" s="4" t="s">
-        <v>105</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="B148" s="4"/>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>107</v>
+        <v>75</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B159" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="B159" s="4" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>122</v>
+        <v>75</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>174</v>
+        <v>121</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" t="s">
-        <v>175</v>
-      </c>
-      <c r="B164" s="16" t="s">
-        <v>176</v>
+      <c r="A164" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" t="s">
+        <v>172</v>
+      </c>
+      <c r="B165" s="16" t="s">
+        <v>173</v>
       </c>
     </row>
   </sheetData>

--- a/Tweaks/Web Browsers Configuration/Firefox/about.config firefox.xlsx
+++ b/Tweaks/Web Browsers Configuration/Firefox/about.config firefox.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/50cb2a26af6a7a83/CyberSecHome/Tweaks/Web Browsers Configuration/Firefox/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\CyberSecHome\Tweaks\Web Browsers Configuration\Firefox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{9EE6A70E-23D5-410F-902C-F038E2EDDAEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9ECED37E-BE38-42CB-A9BD-5F62B7EEA00C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{077AC792-B47F-48BD-97C4-C6DCE09C7CF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="187">
   <si>
     <t>privacy.resistFingerprinting</t>
   </si>
@@ -583,13 +583,16 @@
   </si>
   <si>
     <t>For better anti finger print need to change screen scalability to lower. Will set a frame around the screen.</t>
+  </si>
+  <si>
+    <t>browser.startup.page</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -609,6 +612,12 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -686,7 +695,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -724,6 +733,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -740,10 +750,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1191,8 +1197,12 @@
       <c r="C17" s="1"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="3"/>
-      <c r="B18" s="8"/>
+      <c r="A18" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="B18" s="8">
+        <v>0</v>
+      </c>
       <c r="C18" s="1"/>
     </row>
     <row r="19" spans="1:3">

--- a/Tweaks/Web Browsers Configuration/Firefox/about.config firefox.xlsx
+++ b/Tweaks/Web Browsers Configuration/Firefox/about.config firefox.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\CyberSecHome\Tweaks\Web Browsers Configuration\Firefox\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sense\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{077AC792-B47F-48BD-97C4-C6DCE09C7CF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{414BDAB3-7F72-4F5F-8394-302F045B49C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="186">
   <si>
     <t>privacy.resistFingerprinting</t>
   </si>
@@ -76,9 +76,6 @@
   </si>
   <si>
     <t>network.dns.disableIPv6</t>
-  </si>
-  <si>
-    <t>network.dns.disablePrefetch</t>
   </si>
   <si>
     <t>security.OCSP.require</t>
@@ -596,7 +593,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -604,7 +601,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -615,7 +612,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1016,28 +1013,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G165"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="58.3984375" customWidth="1"/>
-    <col min="2" max="2" width="67.86328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="88.9296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="43.3984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.73046875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.86328125" customWidth="1"/>
-    <col min="9" max="9" width="22.73046875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="35.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="58.375" customWidth="1"/>
+    <col min="2" max="2" width="67.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="88.9375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="43.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.875" customWidth="1"/>
+    <col min="9" max="9" width="22.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="35.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1048,7 +1045,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1059,7 +1056,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1070,7 +1067,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1081,7 +1078,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1092,7 +1089,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1103,7 +1100,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1126,7 +1123,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B10" s="8">
         <v>4000000</v>
@@ -1198,7 +1195,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B18" s="8">
         <v>0</v>
@@ -1224,17 +1221,13 @@
       <c r="C20" s="1"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B21" s="8" t="b">
-        <v>0</v>
-      </c>
+      <c r="A21" s="3"/>
+      <c r="B21" s="8"/>
       <c r="C21" s="1"/>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" s="8" t="b">
         <v>1</v>
@@ -1243,16 +1236,16 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C23" s="1"/>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B24" s="8" t="b">
         <v>0</v>
@@ -1261,7 +1254,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B25" s="8" t="b">
         <v>0</v>
@@ -1270,7 +1263,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B26" s="8" t="b">
         <v>0</v>
@@ -1279,7 +1272,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B27" s="8" t="b">
         <v>0</v>
@@ -1288,7 +1281,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B28" s="8" t="b">
         <v>0</v>
@@ -1297,7 +1290,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B29" s="8" t="b">
         <v>0</v>
@@ -1306,7 +1299,7 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B30" s="8" t="b">
         <v>0</v>
@@ -1315,7 +1308,7 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B31" s="8" t="b">
         <v>0</v>
@@ -1324,7 +1317,7 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B32" s="8" t="b">
         <v>0</v>
@@ -1333,7 +1326,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B33" s="8" t="b">
         <v>0</v>
@@ -1342,7 +1335,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B34" s="8" t="b">
         <v>0</v>
@@ -1351,7 +1344,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B35" s="8" t="b">
         <v>0</v>
@@ -1360,7 +1353,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B36" s="8" t="b">
         <v>1</v>
@@ -1369,7 +1362,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B37" s="8" t="b">
         <v>1</v>
@@ -1378,7 +1371,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B38" s="8" t="b">
         <v>1</v>
@@ -1387,7 +1380,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B39" s="8" t="b">
         <v>1</v>
@@ -1396,7 +1389,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B40" s="8" t="b">
         <v>1</v>
@@ -1405,7 +1398,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B41" s="8" t="b">
         <v>1</v>
@@ -1415,7 +1408,7 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B42" s="8" t="b">
         <v>1</v>
@@ -1424,7 +1417,7 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B43" s="8" t="b">
         <v>1</v>
@@ -1433,7 +1426,7 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B44" s="8" t="b">
         <v>1</v>
@@ -1442,7 +1435,7 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B45" s="8" t="b">
         <v>1</v>
@@ -1451,7 +1444,7 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B46" s="8" t="b">
         <v>1</v>
@@ -1460,7 +1453,7 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B47" s="8" t="b">
         <v>1</v>
@@ -1469,7 +1462,7 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B48" s="8" t="b">
         <v>1</v>
@@ -1478,7 +1471,7 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B49" s="8" t="b">
         <v>1</v>
@@ -1487,7 +1480,7 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B50" s="8" t="b">
         <v>0</v>
@@ -1496,18 +1489,18 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B51" s="8" t="b">
         <v>0</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B52" s="8" t="b">
         <v>0</v>
@@ -1516,7 +1509,7 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B53" s="8" t="b">
         <v>0</v>
@@ -1525,7 +1518,7 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B54" s="8" t="b">
         <v>0</v>
@@ -1534,7 +1527,7 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B55" s="8" t="b">
         <v>1</v>
@@ -1543,16 +1536,16 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="C56" s="1"/>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B57" s="8" t="b">
         <v>0</v>
@@ -1561,7 +1554,7 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B58" s="8" t="b">
         <v>1</v>
@@ -1570,7 +1563,7 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B59" s="8" t="b">
         <v>0</v>
@@ -1579,7 +1572,7 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B60" s="8" t="b">
         <v>0</v>
@@ -1588,7 +1581,7 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B61" s="3">
         <v>2</v>
@@ -1597,7 +1590,7 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B62" s="3" t="b">
         <v>0</v>
@@ -1606,18 +1599,18 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B63" s="3">
         <v>1</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B64" s="3" t="b">
         <v>0</v>
@@ -1626,7 +1619,7 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B65" s="3" t="b">
         <v>0</v>
@@ -1635,18 +1628,18 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B66" s="3">
         <v>32</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B67" s="8" t="b">
         <v>1</v>
@@ -1655,7 +1648,7 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B68" s="3" t="b">
         <v>0</v>
@@ -1663,18 +1656,18 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B69" s="9">
         <v>20</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B70" s="3" t="b">
         <v>0</v>
@@ -1682,18 +1675,18 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B71" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C71" s="4" t="s">
         <v>131</v>
-      </c>
-      <c r="B71" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B72" s="8" t="b">
         <v>1</v>
@@ -1701,7 +1694,7 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B73" s="3" t="b">
         <v>0</v>
@@ -1709,7 +1702,7 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B74" s="3" t="b">
         <v>0</v>
@@ -1717,7 +1710,7 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B75" s="3" t="b">
         <v>0</v>
@@ -1725,7 +1718,7 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B76" s="3" t="b">
         <v>0</v>
@@ -1733,7 +1726,7 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B77" s="3" t="b">
         <v>0</v>
@@ -1741,7 +1734,7 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B78" s="3" t="b">
         <v>0</v>
@@ -1749,7 +1742,7 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B79" s="8" t="b">
         <v>1</v>
@@ -1757,7 +1750,7 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B80" s="8" t="b">
         <v>1</v>
@@ -1765,7 +1758,7 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B81" s="8" t="b">
         <v>1</v>
@@ -1773,7 +1766,7 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B82" s="14" t="b">
         <v>0</v>
@@ -1781,23 +1774,23 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="B83" s="13" t="s">
         <v>148</v>
-      </c>
-      <c r="B83" s="13" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B85" s="14" t="b">
         <v>0</v>
@@ -1805,7 +1798,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B86" s="14" t="b">
         <v>0</v>
@@ -1813,7 +1806,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B87" s="14" t="b">
         <v>0</v>
@@ -1821,7 +1814,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B88" s="14" t="b">
         <v>0</v>
@@ -1829,7 +1822,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B89" s="14" t="b">
         <v>0</v>
@@ -1837,15 +1830,15 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B90" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B91" s="14" t="b">
         <v>0</v>
@@ -1853,7 +1846,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B92" s="14" t="b">
         <v>0</v>
@@ -1861,7 +1854,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B93" s="14" t="b">
         <v>0</v>
@@ -1869,15 +1862,15 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B94" s="15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B95" s="14" t="b">
         <v>0</v>
@@ -1885,7 +1878,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B96" s="14" t="b">
         <v>0</v>
@@ -1893,23 +1886,23 @@
     </row>
     <row r="97" spans="1:3">
       <c r="A97" s="13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B97" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" s="13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B98" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B99" s="14" t="b">
         <v>0</v>
@@ -1917,7 +1910,7 @@
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B100" s="14" t="b">
         <v>0</v>
@@ -1925,7 +1918,7 @@
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B101" s="14" t="b">
         <v>0</v>
@@ -1933,7 +1926,7 @@
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B102" s="14" t="b">
         <v>0</v>
@@ -1941,18 +1934,18 @@
     </row>
     <row r="103" spans="1:3">
       <c r="A103" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B103" s="14">
         <v>32</v>
       </c>
       <c r="C103" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B104" s="14" t="b">
         <v>1</v>
@@ -1960,7 +1953,7 @@
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B105" s="14" t="b">
         <v>1</v>
@@ -1968,7 +1961,7 @@
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B106" s="14" t="b">
         <v>0</v>
@@ -1976,7 +1969,7 @@
     </row>
     <row r="107" spans="1:3">
       <c r="A107" s="13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B107" s="14" t="b">
         <v>1</v>
@@ -1984,7 +1977,7 @@
     </row>
     <row r="108" spans="1:3">
       <c r="A108" s="13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B108" s="15">
         <v>2</v>
@@ -1992,7 +1985,7 @@
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B109" s="14" t="b">
         <v>1</v>
@@ -2000,376 +1993,376 @@
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
+        <v>183</v>
+      </c>
+      <c r="B110" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="C110" t="s">
         <v>184</v>
-      </c>
-      <c r="B110" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="C110" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B125" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="B125" s="4" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B126" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="B126" s="4" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B127" s="4" t="s">
         <v>74</v>
-      </c>
-      <c r="B127" s="4" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B128" s="4" t="s">
         <v>76</v>
-      </c>
-      <c r="B128" s="4" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B129" s="4" t="s">
         <v>78</v>
-      </c>
-      <c r="B129" s="4" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B130" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="B130" s="4" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B133" s="4" t="s">
         <v>84</v>
-      </c>
-      <c r="B133" s="4" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B134" s="4" t="s">
         <v>86</v>
-      </c>
-      <c r="B134" s="4" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B137" s="4" t="s">
         <v>90</v>
-      </c>
-      <c r="B137" s="4" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B145" s="4"/>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B146" s="4"/>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B147" s="4"/>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B148" s="4"/>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B149" s="4" t="s">
         <v>103</v>
-      </c>
-      <c r="B149" s="4" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B150" s="4" t="s">
         <v>105</v>
-      </c>
-      <c r="B150" s="4" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B160" s="4" t="s">
         <v>116</v>
-      </c>
-      <c r="B160" s="4" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B163" s="4" t="s">
         <v>120</v>
-      </c>
-      <c r="B163" s="4" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
+        <v>171</v>
+      </c>
+      <c r="B165" s="16" t="s">
         <v>172</v>
-      </c>
-      <c r="B165" s="16" t="s">
-        <v>173</v>
       </c>
     </row>
   </sheetData>
